--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10188"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>App</t>
   </si>
@@ -56,7 +56,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>Placanje_RSD[MOB_ANDROID]</t>
+    <t>Prelogin_SBB_[MOB]</t>
   </si>
   <si>
     <t>C70820</t>
@@ -72,66 +72,6 @@
   </si>
   <si>
     <t>on</t>
-  </si>
-  <si>
-    <t>HomePage_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70821</t>
-  </si>
-  <si>
-    <t>Licni_Podaci[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70822</t>
-  </si>
-  <si>
-    <t>Card_details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70823</t>
-  </si>
-  <si>
-    <t>Offers_overview_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70824</t>
-  </si>
-  <si>
-    <t>Placanje_RSD_Skeniranjem_QR[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70825</t>
-  </si>
-  <si>
-    <t>Internal_transfer_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70826</t>
-  </si>
-  <si>
-    <t>Accounts-Domestic_Accounts-Change_name_of_account_[MOB]</t>
-  </si>
-  <si>
-    <t>C70827</t>
-  </si>
-  <si>
-    <t>Accounts-Domestic_Accounts-Change_name_of_account_to_default_[MOB]</t>
-  </si>
-  <si>
-    <t>C70828</t>
-  </si>
-  <si>
-    <t>Accounts-Foreign_Accounts-Change_name_of_account_[MOB]</t>
-  </si>
-  <si>
-    <t>Accounts-Foreign_Accounts-Change_name_of_account_to_default_[MOB]</t>
-  </si>
-  <si>
-    <t>Homepage_Bottom_nav_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>Homepage_Account_Display_[ANDROID_MOB]</t>
   </si>
 </sst>
 </file>
@@ -503,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -521,39 +461,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -681,7 +588,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -693,34 +600,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -805,16 +712,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1146,8 +1050,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1199,299 +1103,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G12" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G2" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C15:C1048576">
+  <conditionalFormatting sqref="C1 C3:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
